--- a/artfynd/A 251-2026 artfynd.xlsx
+++ b/artfynd/A 251-2026 artfynd.xlsx
@@ -787,7 +787,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130609987</v>
+        <v>130610001</v>
       </c>
       <c r="B3" t="n">
         <v>57852</v>
@@ -818,14 +818,14 @@
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Tallåsberget, Vb</t>
+          <t>Lill-Gröndiket, Vb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>745226</v>
+        <v>745103</v>
       </c>
       <c r="R3" t="n">
-        <v>7101508</v>
+        <v>7101542</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -857,7 +857,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -867,12 +867,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,7 +899,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130610001</v>
+        <v>130609987</v>
       </c>
       <c r="B4" t="n">
         <v>57852</v>
@@ -930,14 +930,14 @@
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Lill-Gröndiket, Vb</t>
+          <t>Tallåsberget, Vb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>745103</v>
+        <v>745226</v>
       </c>
       <c r="R4" t="n">
-        <v>7101542</v>
+        <v>7101508</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -969,7 +969,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -979,12 +979,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 251-2026 artfynd.xlsx
+++ b/artfynd/A 251-2026 artfynd.xlsx
@@ -1119,10 +1119,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130610005</v>
+        <v>130610000</v>
       </c>
       <c r="B6" t="n">
-        <v>91777</v>
+        <v>57852</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1130,30 +1130,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Tallåsberget, Vb</t>
+          <t>Lill-Gröndiket, Vb</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>745224</v>
+        <v>745080</v>
       </c>
       <c r="R6" t="n">
-        <v>7101586</v>
+        <v>7101519</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,7 +1189,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1195,7 +1199,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>11:04</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1222,10 +1231,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130610000</v>
+        <v>130610005</v>
       </c>
       <c r="B7" t="n">
-        <v>57852</v>
+        <v>91778</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1233,34 +1242,30 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Lill-Gröndiket, Vb</t>
+          <t>Tallåsberget, Vb</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>745080</v>
+        <v>745224</v>
       </c>
       <c r="R7" t="n">
-        <v>7101519</v>
+        <v>7101586</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1292,7 +1297,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1302,12 +1307,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:04</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AD7" t="b">

--- a/artfynd/A 251-2026 artfynd.xlsx
+++ b/artfynd/A 251-2026 artfynd.xlsx
@@ -1119,10 +1119,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130610000</v>
+        <v>130610005</v>
       </c>
       <c r="B6" t="n">
-        <v>57852</v>
+        <v>91779</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1130,34 +1130,30 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Lill-Gröndiket, Vb</t>
+          <t>Tallåsberget, Vb</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>745080</v>
+        <v>745224</v>
       </c>
       <c r="R6" t="n">
-        <v>7101519</v>
+        <v>7101586</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1189,7 +1185,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1199,12 +1195,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:04</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1231,10 +1222,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130610005</v>
+        <v>130610000</v>
       </c>
       <c r="B7" t="n">
-        <v>91778</v>
+        <v>57852</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1242,30 +1233,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Tallåsberget, Vb</t>
+          <t>Lill-Gröndiket, Vb</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>745224</v>
+        <v>745080</v>
       </c>
       <c r="R7" t="n">
-        <v>7101586</v>
+        <v>7101519</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1297,7 +1292,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1307,7 +1302,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>11:04</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD7" t="b">

--- a/artfynd/A 251-2026 artfynd.xlsx
+++ b/artfynd/A 251-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130609990</v>
       </c>
       <c r="B2" t="n">
-        <v>57852</v>
+        <v>57854</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>130610001</v>
       </c>
       <c r="B3" t="n">
-        <v>57852</v>
+        <v>57854</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
         <v>130609987</v>
       </c>
       <c r="B4" t="n">
-        <v>57852</v>
+        <v>57854</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1014,7 +1014,7 @@
         <v>130609991</v>
       </c>
       <c r="B5" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1122,7 +1122,7 @@
         <v>130610005</v>
       </c>
       <c r="B6" t="n">
-        <v>91779</v>
+        <v>91781</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1225,7 +1225,7 @@
         <v>130610000</v>
       </c>
       <c r="B7" t="n">
-        <v>57852</v>
+        <v>57854</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1337,7 +1337,7 @@
         <v>130609988</v>
       </c>
       <c r="B8" t="n">
-        <v>57852</v>
+        <v>57854</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1449,7 +1449,7 @@
         <v>130609994</v>
       </c>
       <c r="B9" t="n">
-        <v>57852</v>
+        <v>57854</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1561,7 +1561,7 @@
         <v>130609996</v>
       </c>
       <c r="B10" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1668,7 +1668,7 @@
         <v>130610006</v>
       </c>
       <c r="B11" t="n">
-        <v>57852</v>
+        <v>57854</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1780,7 +1780,7 @@
         <v>130610003</v>
       </c>
       <c r="B12" t="n">
-        <v>57852</v>
+        <v>57854</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 251-2026 artfynd.xlsx
+++ b/artfynd/A 251-2026 artfynd.xlsx
@@ -1119,10 +1119,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130610005</v>
+        <v>130610000</v>
       </c>
       <c r="B6" t="n">
-        <v>91781</v>
+        <v>57854</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1130,30 +1130,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Tallåsberget, Vb</t>
+          <t>Lill-Gröndiket, Vb</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>745224</v>
+        <v>745080</v>
       </c>
       <c r="R6" t="n">
-        <v>7101586</v>
+        <v>7101519</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,7 +1189,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1195,7 +1199,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>11:04</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1222,10 +1231,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130610000</v>
+        <v>130610005</v>
       </c>
       <c r="B7" t="n">
-        <v>57854</v>
+        <v>91781</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1233,34 +1242,30 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Lill-Gröndiket, Vb</t>
+          <t>Tallåsberget, Vb</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>745080</v>
+        <v>745224</v>
       </c>
       <c r="R7" t="n">
-        <v>7101519</v>
+        <v>7101586</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1292,7 +1297,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1302,12 +1307,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:04</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AD7" t="b">

--- a/artfynd/A 251-2026 artfynd.xlsx
+++ b/artfynd/A 251-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130609990</v>
       </c>
       <c r="B2" t="n">
-        <v>57854</v>
+        <v>57862</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130610001</v>
+        <v>130609987</v>
       </c>
       <c r="B3" t="n">
-        <v>57854</v>
+        <v>57862</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -818,14 +818,14 @@
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Lill-Gröndiket, Vb</t>
+          <t>Tallåsberget, Vb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>745103</v>
+        <v>745226</v>
       </c>
       <c r="R3" t="n">
-        <v>7101542</v>
+        <v>7101508</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -857,7 +857,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -867,12 +867,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130609987</v>
+        <v>130610001</v>
       </c>
       <c r="B4" t="n">
-        <v>57854</v>
+        <v>57862</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -930,14 +930,14 @@
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Tallåsberget, Vb</t>
+          <t>Lill-Gröndiket, Vb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>745226</v>
+        <v>745103</v>
       </c>
       <c r="R4" t="n">
-        <v>7101508</v>
+        <v>7101542</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -969,7 +969,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -979,12 +979,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1014,7 +1014,7 @@
         <v>130609991</v>
       </c>
       <c r="B5" t="n">
-        <v>79211</v>
+        <v>79219</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1119,10 +1119,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130610000</v>
+        <v>130610005</v>
       </c>
       <c r="B6" t="n">
-        <v>57854</v>
+        <v>91794</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1130,34 +1130,30 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Lill-Gröndiket, Vb</t>
+          <t>Tallåsberget, Vb</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>745080</v>
+        <v>745224</v>
       </c>
       <c r="R6" t="n">
-        <v>7101519</v>
+        <v>7101586</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1189,7 +1185,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1199,12 +1195,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:04</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1231,10 +1222,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130610005</v>
+        <v>130610000</v>
       </c>
       <c r="B7" t="n">
-        <v>91781</v>
+        <v>57862</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1242,30 +1233,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Tallåsberget, Vb</t>
+          <t>Lill-Gröndiket, Vb</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>745224</v>
+        <v>745080</v>
       </c>
       <c r="R7" t="n">
-        <v>7101586</v>
+        <v>7101519</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1297,7 +1292,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1307,7 +1302,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>11:04</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1337,7 +1337,7 @@
         <v>130609988</v>
       </c>
       <c r="B8" t="n">
-        <v>57854</v>
+        <v>57862</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1449,7 +1449,7 @@
         <v>130609994</v>
       </c>
       <c r="B9" t="n">
-        <v>57854</v>
+        <v>57862</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1561,7 +1561,7 @@
         <v>130609996</v>
       </c>
       <c r="B10" t="n">
-        <v>79211</v>
+        <v>79219</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1668,7 +1668,7 @@
         <v>130610006</v>
       </c>
       <c r="B11" t="n">
-        <v>57854</v>
+        <v>57862</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1780,7 +1780,7 @@
         <v>130610003</v>
       </c>
       <c r="B12" t="n">
-        <v>57854</v>
+        <v>57862</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 251-2026 artfynd.xlsx
+++ b/artfynd/A 251-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130609990</v>
       </c>
       <c r="B2" t="n">
-        <v>57862</v>
+        <v>57863</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130609987</v>
+        <v>130610001</v>
       </c>
       <c r="B3" t="n">
-        <v>57862</v>
+        <v>57863</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -818,14 +818,14 @@
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Tallåsberget, Vb</t>
+          <t>Lill-Gröndiket, Vb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>745226</v>
+        <v>745103</v>
       </c>
       <c r="R3" t="n">
-        <v>7101508</v>
+        <v>7101542</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -857,7 +857,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -867,12 +867,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130610001</v>
+        <v>130609987</v>
       </c>
       <c r="B4" t="n">
-        <v>57862</v>
+        <v>57863</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -930,14 +930,14 @@
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Lill-Gröndiket, Vb</t>
+          <t>Tallåsberget, Vb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>745103</v>
+        <v>745226</v>
       </c>
       <c r="R4" t="n">
-        <v>7101542</v>
+        <v>7101508</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -969,7 +969,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -979,12 +979,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1014,7 +1014,7 @@
         <v>130609991</v>
       </c>
       <c r="B5" t="n">
-        <v>79219</v>
+        <v>79220</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1119,10 +1119,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130610005</v>
+        <v>130610000</v>
       </c>
       <c r="B6" t="n">
-        <v>91794</v>
+        <v>57863</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1130,30 +1130,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Tallåsberget, Vb</t>
+          <t>Lill-Gröndiket, Vb</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>745224</v>
+        <v>745080</v>
       </c>
       <c r="R6" t="n">
-        <v>7101586</v>
+        <v>7101519</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,7 +1189,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1195,7 +1199,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>11:04</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1222,10 +1231,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130610000</v>
+        <v>130610005</v>
       </c>
       <c r="B7" t="n">
-        <v>57862</v>
+        <v>91795</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1233,34 +1242,30 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Lill-Gröndiket, Vb</t>
+          <t>Tallåsberget, Vb</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>745080</v>
+        <v>745224</v>
       </c>
       <c r="R7" t="n">
-        <v>7101519</v>
+        <v>7101586</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1292,7 +1297,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1302,12 +1307,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:04</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1337,7 +1337,7 @@
         <v>130609988</v>
       </c>
       <c r="B8" t="n">
-        <v>57862</v>
+        <v>57863</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1449,7 +1449,7 @@
         <v>130609994</v>
       </c>
       <c r="B9" t="n">
-        <v>57862</v>
+        <v>57863</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1561,7 +1561,7 @@
         <v>130609996</v>
       </c>
       <c r="B10" t="n">
-        <v>79219</v>
+        <v>79220</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1668,7 +1668,7 @@
         <v>130610006</v>
       </c>
       <c r="B11" t="n">
-        <v>57862</v>
+        <v>57863</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1780,7 +1780,7 @@
         <v>130610003</v>
       </c>
       <c r="B12" t="n">
-        <v>57862</v>
+        <v>57863</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 251-2026 artfynd.xlsx
+++ b/artfynd/A 251-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130609990</v>
       </c>
       <c r="B2" t="n">
-        <v>57863</v>
+        <v>57864</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>130610001</v>
       </c>
       <c r="B3" t="n">
-        <v>57863</v>
+        <v>57864</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
         <v>130609987</v>
       </c>
       <c r="B4" t="n">
-        <v>57863</v>
+        <v>57864</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1014,7 +1014,7 @@
         <v>130609991</v>
       </c>
       <c r="B5" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1119,10 +1119,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130610000</v>
+        <v>130610005</v>
       </c>
       <c r="B6" t="n">
-        <v>57863</v>
+        <v>91796</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1130,34 +1130,30 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Lill-Gröndiket, Vb</t>
+          <t>Tallåsberget, Vb</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>745080</v>
+        <v>745224</v>
       </c>
       <c r="R6" t="n">
-        <v>7101519</v>
+        <v>7101586</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1189,7 +1185,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1199,12 +1195,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:04</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1231,10 +1222,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130610005</v>
+        <v>130610000</v>
       </c>
       <c r="B7" t="n">
-        <v>91795</v>
+        <v>57864</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1242,30 +1233,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Tallåsberget, Vb</t>
+          <t>Lill-Gröndiket, Vb</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>745224</v>
+        <v>745080</v>
       </c>
       <c r="R7" t="n">
-        <v>7101586</v>
+        <v>7101519</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1297,7 +1292,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1307,7 +1302,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>11:04</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1337,7 +1337,7 @@
         <v>130609988</v>
       </c>
       <c r="B8" t="n">
-        <v>57863</v>
+        <v>57864</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1449,7 +1449,7 @@
         <v>130609994</v>
       </c>
       <c r="B9" t="n">
-        <v>57863</v>
+        <v>57864</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1561,7 +1561,7 @@
         <v>130609996</v>
       </c>
       <c r="B10" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1668,7 +1668,7 @@
         <v>130610006</v>
       </c>
       <c r="B11" t="n">
-        <v>57863</v>
+        <v>57864</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1780,7 +1780,7 @@
         <v>130610003</v>
       </c>
       <c r="B12" t="n">
-        <v>57863</v>
+        <v>57864</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 251-2026 artfynd.xlsx
+++ b/artfynd/A 251-2026 artfynd.xlsx
@@ -1119,10 +1119,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130610005</v>
+        <v>130610000</v>
       </c>
       <c r="B6" t="n">
-        <v>91796</v>
+        <v>57864</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1130,30 +1130,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Tallåsberget, Vb</t>
+          <t>Lill-Gröndiket, Vb</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>745224</v>
+        <v>745080</v>
       </c>
       <c r="R6" t="n">
-        <v>7101586</v>
+        <v>7101519</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,7 +1189,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1195,7 +1199,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>11:04</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1222,10 +1231,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130610000</v>
+        <v>130610005</v>
       </c>
       <c r="B7" t="n">
-        <v>57864</v>
+        <v>91796</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1233,34 +1242,30 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Lill-Gröndiket, Vb</t>
+          <t>Tallåsberget, Vb</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>745080</v>
+        <v>745224</v>
       </c>
       <c r="R7" t="n">
-        <v>7101519</v>
+        <v>7101586</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1292,7 +1297,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1302,12 +1307,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:04</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AD7" t="b">

--- a/artfynd/A 251-2026 artfynd.xlsx
+++ b/artfynd/A 251-2026 artfynd.xlsx
@@ -1119,10 +1119,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130610000</v>
+        <v>130610005</v>
       </c>
       <c r="B6" t="n">
-        <v>57864</v>
+        <v>91796</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1130,34 +1130,30 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Lill-Gröndiket, Vb</t>
+          <t>Tallåsberget, Vb</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>745080</v>
+        <v>745224</v>
       </c>
       <c r="R6" t="n">
-        <v>7101519</v>
+        <v>7101586</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1189,7 +1185,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1199,12 +1195,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:04</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1231,10 +1222,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130610005</v>
+        <v>130610000</v>
       </c>
       <c r="B7" t="n">
-        <v>91796</v>
+        <v>57864</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1242,30 +1233,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Tallåsberget, Vb</t>
+          <t>Lill-Gröndiket, Vb</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>745224</v>
+        <v>745080</v>
       </c>
       <c r="R7" t="n">
-        <v>7101586</v>
+        <v>7101519</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1297,7 +1292,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1307,7 +1302,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>11:04</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD7" t="b">

--- a/artfynd/A 251-2026 artfynd.xlsx
+++ b/artfynd/A 251-2026 artfynd.xlsx
@@ -1122,7 +1122,7 @@
         <v>130610005</v>
       </c>
       <c r="B6" t="n">
-        <v>91796</v>
+        <v>91804</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 251-2026 artfynd.xlsx
+++ b/artfynd/A 251-2026 artfynd.xlsx
@@ -787,7 +787,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130610001</v>
+        <v>130609987</v>
       </c>
       <c r="B3" t="n">
         <v>57864</v>
@@ -818,14 +818,14 @@
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Lill-Gröndiket, Vb</t>
+          <t>Tallåsberget, Vb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>745103</v>
+        <v>745226</v>
       </c>
       <c r="R3" t="n">
-        <v>7101542</v>
+        <v>7101508</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -857,7 +857,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -867,12 +867,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,7 +899,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130609987</v>
+        <v>130610001</v>
       </c>
       <c r="B4" t="n">
         <v>57864</v>
@@ -930,14 +930,14 @@
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Tallåsberget, Vb</t>
+          <t>Lill-Gröndiket, Vb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>745226</v>
+        <v>745103</v>
       </c>
       <c r="R4" t="n">
-        <v>7101508</v>
+        <v>7101542</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -969,7 +969,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -979,12 +979,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 251-2026 artfynd.xlsx
+++ b/artfynd/A 251-2026 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130609990</v>
+        <v>130609991</v>
       </c>
       <c r="B2" t="n">
-        <v>57884</v>
+        <v>79327</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>745242</v>
+        <v>745226</v>
       </c>
       <c r="R2" t="n">
-        <v>7101432</v>
+        <v>7101434</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -758,17 +758,13 @@
           <t>11:31</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -787,45 +783,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130610001</v>
+        <v>130609996</v>
       </c>
       <c r="B3" t="n">
-        <v>57884</v>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Lill-Gröndiket, Vb</t>
+          <t>Tallåsberget, Vb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>745103</v>
+        <v>745221</v>
       </c>
       <c r="R3" t="n">
-        <v>7101542</v>
+        <v>7101438</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -857,7 +853,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -867,12 +863,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:00</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,32 +890,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130609987</v>
+        <v>130609999</v>
       </c>
       <c r="B4" t="n">
-        <v>57884</v>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -934,10 +925,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>745226</v>
+        <v>745124</v>
       </c>
       <c r="R4" t="n">
-        <v>7101508</v>
+        <v>7101510</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -969,7 +960,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -979,12 +970,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:39</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,10 +997,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130609991</v>
+        <v>130609987</v>
       </c>
       <c r="B5" t="n">
-        <v>79243</v>
+        <v>57953</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1022,21 +1008,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1049,7 +1035,7 @@
         <v>745226</v>
       </c>
       <c r="R5" t="n">
-        <v>7101434</v>
+        <v>7101508</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1081,7 +1067,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1091,7 +1077,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>11:39</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1100,7 +1091,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1119,10 +1109,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130610005</v>
+        <v>130609988</v>
       </c>
       <c r="B6" t="n">
-        <v>91828</v>
+        <v>57953</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1130,19 +1120,23 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1150,10 +1144,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>745224</v>
+        <v>745260</v>
       </c>
       <c r="R6" t="n">
-        <v>7101586</v>
+        <v>7101421</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,7 +1179,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1195,7 +1189,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>11:35</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1222,10 +1221,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130610000</v>
+        <v>130609990</v>
       </c>
       <c r="B7" t="n">
-        <v>57884</v>
+        <v>57953</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1253,14 +1252,14 @@
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Lill-Gröndiket, Vb</t>
+          <t>Tallåsberget, Vb</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>745080</v>
+        <v>745242</v>
       </c>
       <c r="R7" t="n">
-        <v>7101519</v>
+        <v>7101432</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1292,7 +1291,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1302,12 +1301,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1334,10 +1333,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130609988</v>
+        <v>130609994</v>
       </c>
       <c r="B8" t="n">
-        <v>57884</v>
+        <v>57953</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1369,10 +1368,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>745260</v>
+        <v>745213</v>
       </c>
       <c r="R8" t="n">
-        <v>7101421</v>
+        <v>7101435</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1404,7 +1403,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1414,7 +1413,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -1446,10 +1445,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130609994</v>
+        <v>130610000</v>
       </c>
       <c r="B9" t="n">
-        <v>57884</v>
+        <v>57953</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1477,14 +1476,14 @@
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Tallåsberget, Vb</t>
+          <t>Lill-Gröndiket, Vb</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>745213</v>
+        <v>745080</v>
       </c>
       <c r="R9" t="n">
-        <v>7101435</v>
+        <v>7101519</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1516,7 +1515,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1526,12 +1525,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1558,10 +1557,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130609996</v>
+        <v>130610001</v>
       </c>
       <c r="B10" t="n">
-        <v>79243</v>
+        <v>57953</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1569,34 +1568,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Tallåsberget, Vb</t>
+          <t>Lill-Gröndiket, Vb</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>745221</v>
+        <v>745103</v>
       </c>
       <c r="R10" t="n">
-        <v>7101438</v>
+        <v>7101542</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1628,7 +1627,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1638,7 +1637,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1665,10 +1669,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130610006</v>
+        <v>130610003</v>
       </c>
       <c r="B11" t="n">
-        <v>57884</v>
+        <v>57953</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1694,16 +1698,20 @@
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Tallåsberget, Vb</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>745229</v>
+        <v>745224</v>
       </c>
       <c r="R11" t="n">
-        <v>7101588</v>
+        <v>7101573</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1735,7 +1743,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1745,7 +1753,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
@@ -1777,10 +1785,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130610003</v>
+        <v>130610006</v>
       </c>
       <c r="B12" t="n">
-        <v>57884</v>
+        <v>57953</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1806,20 +1814,16 @@
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Tallåsberget, Vb</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>745224</v>
+        <v>745229</v>
       </c>
       <c r="R12" t="n">
-        <v>7101573</v>
+        <v>7101588</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1851,7 +1855,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1861,7 +1865,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">

--- a/artfynd/A 251-2026 artfynd.xlsx
+++ b/artfynd/A 251-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AZ12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -780,6 +785,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130609991</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -887,6 +897,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130609996</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -994,6 +1009,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130609999</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1106,6 +1126,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130609987</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1218,6 +1243,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130609988</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1330,6 +1360,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130609990</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1442,6 +1477,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130609994</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1554,6 +1594,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130610000</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1666,6 +1711,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130610001</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1782,6 +1832,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130610003</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1894,8 +1949,26 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130610006</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>